--- a/astro-site/public/dl/kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura del Negocio" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre del Negocio" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura del Negocio" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre del Negocio" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Area">'Instrucciones'!$A$1:$A$20</definedName>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Apertura del Negocio'!$A$1:$H$24</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Cierre del Negocio'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +76,11 @@
       <i val="1"/>
       <color rgb="00888888"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -140,51 +145,62 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -544,122 +560,131 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="80"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>AI Chef Pro — aichef.pro</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="30" r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Kit de Tareas — Chocolatería / Bombonería</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="25" r="3">
+    <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Checklist de Apertura y Cierre del Negocio</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="35" r="5">
+    <row r="4"/>
+    <row r="5" ht="35" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>📋 Instrucciones de Uso</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>1. Este archivo contiene checklists profesionales para la apertura y cierre de tu negocio.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2. Imprime las hojas que necesites o úsalas en formato digital (tablet/ordenador).</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>3. Cada checklist incluye columnas para marcar tareas completadas, responsable, hora y notas.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>4. Personaliza las tareas según las necesidades específicas de tu establecimiento.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>5. Añade o elimina filas según tu operativa diaria.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>6. Usa la validación de datos en la columna '✓ Completada' para marcar el estado.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>7. Rellena la firma y fecha cada día para mantener el control.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>💡 Consejo: Plastifica una copia impresa y usa rotuladores borrables para reutilizarla cada día.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>© AI Chef Pro — aichef.pro</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>29 años de experiencia en alta hostelería · 15 años de consultoría gastronómica</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="18">
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -667,7 +692,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -681,24 +715,24 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="13"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="25"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Apertura del Negocio — Chocolatería / Bombonería</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fecha: ____/____/________</t>
@@ -710,8 +744,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
@@ -753,7 +787,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -773,7 +807,7 @@
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -793,7 +827,7 @@
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
@@ -813,7 +847,7 @@
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -833,7 +867,7 @@
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
@@ -853,7 +887,7 @@
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -873,7 +907,7 @@
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="11">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
@@ -893,7 +927,7 @@
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="12">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -913,7 +947,7 @@
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="13">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
@@ -933,7 +967,7 @@
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -953,7 +987,7 @@
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
@@ -973,7 +1007,7 @@
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="16">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
@@ -993,7 +1027,7 @@
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="17">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
@@ -1013,7 +1047,7 @@
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="18">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>14</v>
       </c>
@@ -1033,7 +1067,7 @@
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="19">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
@@ -1053,7 +1087,7 @@
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="20">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>16</v>
       </c>
@@ -1073,7 +1107,7 @@
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="21">
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="8" t="n">
         <v>17</v>
       </c>
@@ -1093,7 +1127,27 @@
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="30" r="23">
+    <row r="22">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C22">
+        <f>COUNTIF(F5:F21,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E22">
+        <f>COUNTIF(B5:B21,"?*")</f>
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
@@ -1115,13 +1169,18 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A23:H23"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:H21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona ✓, ✗ o —" errorTitle="Valor no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1135,24 +1194,24 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="13"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="25"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cierre del Negocio — Chocolatería / Bombonería</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fecha: ____/____/________</t>
@@ -1164,8 +1223,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
@@ -1207,7 +1266,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -1227,7 +1286,7 @@
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -1247,7 +1306,7 @@
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
@@ -1267,7 +1326,7 @@
       <c r="G7" s="8" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -1287,7 +1346,7 @@
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
@@ -1307,7 +1366,7 @@
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -1327,7 +1386,7 @@
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="11">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
@@ -1347,7 +1406,7 @@
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="12">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -1367,7 +1426,7 @@
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="13">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
@@ -1387,7 +1446,7 @@
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -1407,7 +1466,7 @@
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
@@ -1427,7 +1486,7 @@
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="16">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
@@ -1447,7 +1506,7 @@
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="17">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
@@ -1467,7 +1526,7 @@
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="18">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>14</v>
       </c>
@@ -1487,7 +1546,7 @@
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="11" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="19">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
@@ -1507,7 +1566,27 @@
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="30" r="21">
+    <row r="20">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>COUNTIF(F5:F19,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>COUNTIF(B5:B19,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
@@ -1529,12 +1608,17 @@
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:H19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona ✓, ✗ o —" errorTitle="Valor no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx
@@ -13,7 +13,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura del Negocio'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre del Negocio'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -710,7 +712,7 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
@@ -1179,8 +1181,16 @@
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1189,7 +1199,7 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
@@ -1618,7 +1628,15 @@
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre del Negocio" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura del Negocio'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura del Negocio'!$A$1:$H$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre del Negocio'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre del Negocio'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +84,22 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +136,11 @@
         <bgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -149,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -188,6 +207,39 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -564,136 +616,239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AI Chef Pro — aichef.pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Kit de Tareas — Chocolatería / Bombonería</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Checklist de Apertura y Cierre del Negocio</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>📋 Instrucciones de Uso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>1. Este archivo contiene checklists profesionales para la apertura y cierre de tu negocio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2. Imprime las hojas que necesites o úsalas en formato digital (tablet/ordenador).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>3. Cada checklist incluye columnas para marcar tareas completadas, responsable, hora y notas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>4. Personaliza las tareas según las necesidades específicas de tu establecimiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>5. Añade o elimina filas según tu operativa diaria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>6. Usa la validación de datos en la columna '✓ Completada' para marcar el estado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>7. Rellena la firma y fecha cada día para mantener el control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>💡 Consejo: Plastifica una copia impresa y usa rotuladores borrables para reutilizarla cada día.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Apertura y Cierre del Negocio — Chocolatería / Bombonería</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Qué resuelve</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>▸ Es el checklist del LOCAL COMPLETO: lo que se abre y se cierra del negocio entero, no de cada área. Úsalo como marco del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Cómo usar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>▸ Imprime la hoja del turno (apertura o cierre) o úsala en tablet; el responsable reparte y cada persona firma su tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>▸ Cada tarea trae Responsable y Hora Límite precargados con el criterio del kit: ajústalos a tu horario real, son celdas verdes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Celdas editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>▸ Todo lo que se rellena a diario va en VERDE: Responsable, Hora Límite, ✓ Completada, Firma y Notas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar) y el de caja lleva el DINERO. Si una tarea aparece en los dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>▸ Estás en 08-apertura-cierre-negocio.xlsx: este ES el marco del día — el HITO de abrir y cerrar el local; el DINERO, en 09-apertura-cierre-caja.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Chocolatería / Bombonería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="35" customHeight="1">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>Contacto: info@aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1"/>
-  </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -714,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -790,399 +945,588 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Desactivar alarma del local</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Encender luces generales (interior y exterior)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Encender climatización (HVAC) / calefacción según temporada</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Abrir persianas / puerta principal</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Montar señalización exterior / pizarra de menú</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Montar la señalización exterior y el cartel de encargos por adelantado, y comprobar que al escaparate no le da el sol directo: el chocolate expuesto se funde y pierde el brillo</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Exterior</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Encender TPV / POS / datáfono</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Caja</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="11" t="inlineStr"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Encender sistema de reservas / tablet de pedidos</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Recepción</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Encender las vitrinas temperadas de bombones y tabletas nada más entrar: tardan en bajar y el género no se monta hasta que estén en rango</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Poner música ambiente al volumen adecuado</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Revisar reservas del día y eventos especiales</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Recepción</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr"/>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Revisar los encargos comprometidos para hoy: unidades, hora de recogida y quién los prepara, y dejar preparadas las cajas de regalo y las cintas de los que se recojan por la mañana</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Mostrador</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Comprobar baños: papel, jabón, limpieza, ambientador</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Verificar limpieza de zonas comunes (entrada, pasillos)</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Zonas comunes</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Revisar estado del mobiliario (sillas, mesas, iluminación)</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Revisar el estado del mobiliario de tienda: mostrador, estanterías y escaparate sin desperfectos, sin bombillas fundidas y sin cristales rayados</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr"/>
+      <c r="G16" s="19" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Montar terraza si aplica (mesas, sillas, sombrillas/estufas)</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr"/>
+      <c r="G17" s="19" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Comprobar que las cartas/menús están en orden</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Sala</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr"/>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Comprobar antes de abrir que ninguna bandeja de la vitrina se queda sin su etiqueta de precio (y sin el precio por kilo, si se vende al peso) ni sin sus alérgenos a la vista, y que hay repuesto en cámara para reponer durante el día</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Encender displays / pantallas informativas si las hay</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr"/>
+      <c r="G19" s="19" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Encender vitrinas temperadas</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Tienda</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="10" t="inlineStr"/>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="8" t="n">
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 °C y menos del 55 % de humedad antes de montar el género — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr"/>
+      <c r="G20" s="19" t="inlineStr"/>
+      <c r="H20" s="20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Verificar temperatura obrador (18-20°C)</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Verificar la temperatura y la humedad del obrador: objetivo 18-20 °C y 50-60 % — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr"/>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr"/>
+      <c r="G21" s="19" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="B22" s="13" t="inlineStr">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="20" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C22">
-        <f>COUNTIF(F5:F21,"✓")</f>
+      <c r="D28">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E22">
-        <f>COUNTIF(B5:B21,"?*")</f>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
         <v>17.0</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Chocolatería / Bombonería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H21">
+  <conditionalFormatting sqref="A5:H26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
@@ -1201,7 +1545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1257,7 +1601,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1277,359 +1621,532 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Apagar música ambiente</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Verificar que no quedan clientes en el local</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Limpiar y recoger terraza si aplica</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Apagar TPV / POS / datáfono (o dejar en standby)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Caja</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="11" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Cerrar persianas y puertas</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Apagar luces (dejar mínimas de seguridad)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="11" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Apagar climatización</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Recoger señalización exterior</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Exterior</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Comprobar que ventanas están cerradas</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr"/>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Vaciar papeleras de zonas comunes y baños</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Baños</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr"/>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Revisión final de seguridad (gas, agua, enchufes)</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Activar alarma</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="11" t="inlineStr"/>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr"/>
+      <c r="G16" s="19" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Cerrar con llave y verificar cierre</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Último en salir</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr"/>
+      <c r="G17" s="19" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Apagar vitrinas temperadas</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Tienda</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Apagar las vitrinas temperadas una vez retirado el género a la cámara de conservación</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Último en salir</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr"/>
+      <c r="G18" s="19" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Registrar temperatura de cierre del obrador</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Registrar la temperatura de cierre del obrador: objetivo 18-20 °C — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Obrador</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="9" t="inlineStr"/>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Último en salir</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr"/>
+      <c r="G19" s="19" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="inlineStr">
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="20" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="20" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C20">
-        <f>COUNTIF(F5:F19,"✓")</f>
+      <c r="D26">
+        <f>COUNTIFS(B5:B24,"?*",F5:F24,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E20">
-        <f>COUNTIF(B5:B19,"?*")</f>
+      <c r="F26">
+        <f>COUNTIF(B5:B24,"?*")-COUNTIF(F5:F24,"N/A")</f>
         <v>15.0</v>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora de finalización: ________</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Chocolatería / Bombonería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H19">
+  <conditionalFormatting sqref="A5:H24">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>

--- a/astro-site/public/dl/kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx
@@ -630,7 +630,7 @@
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Apertura y Cierre del Negocio — Chocolatería / Bombonería</t>
+          <t>Apertura y Cierre del Negocio — Chocolatería</t>
         </is>
       </c>
     </row>
@@ -743,6 +743,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="18" customHeight="1">
       <c r="B23" s="15" t="inlineStr">
         <is>
@@ -750,6 +751,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="32" customHeight="1">
       <c r="B25" s="16" t="inlineStr">
         <is>
@@ -764,6 +766,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="15" t="inlineStr">
         <is>
@@ -771,6 +774,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="32" customHeight="1">
       <c r="B30" s="16" t="inlineStr">
         <is>
@@ -785,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="15" t="inlineStr">
         <is>
@@ -792,6 +797,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="16" customHeight="1">
       <c r="B35" s="16" t="inlineStr">
         <is>
@@ -820,13 +826,15 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>— Kit de Tareas Recurrentes · Chocolatería / Bombonería · AI Chef Pro · aichef.pro</t>
-        </is>
-      </c>
-    </row>
+          <t>— Kit de Tareas Recurrentes · Chocolatería · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42" ht="35" customHeight="1">
       <c r="B42" s="15" t="inlineStr">
         <is>
@@ -841,6 +849,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="15" t="inlineStr">
         <is>
@@ -1501,7 +1510,7 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>— Kit de Tareas Recurrentes · Chocolatería / Bombonería · AI Chef Pro · aichef.pro</t>
+          <t>— Kit de Tareas Recurrentes · Chocolatería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2130,7 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>— Kit de Tareas Recurrentes · Chocolatería / Bombonería · AI Chef Pro · aichef.pro</t>
+          <t>— Kit de Tareas Recurrentes · Chocolatería · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
